--- a/DocPages.xlsx
+++ b/DocPages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\awsles\AwsServices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9F8FB2-68B9-4F68-8B13-A07F035E3FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{951CD3E3-6E30-4D59-86B1-4AE3A584FAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17184" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{36A64E5D-0A85-4E61-A89B-32179BC889B1}"/>
+    <workbookView xWindow="315" yWindow="593" windowWidth="20250" windowHeight="12239" xr2:uid="{36A64E5D-0A85-4E61-A89B-32179BC889B1}"/>
   </bookViews>
   <sheets>
     <sheet name="DocPages" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="AwsServices-Temp" sheetId="2" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DocPages!$A$1:$D$478</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DocPages!$A$1:$D$479</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DocPages (DEV)'!$A$1:$G$478</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6338" uniqueCount="3465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6342" uniqueCount="3469">
   <si>
     <t>ServiceName</t>
   </si>
@@ -10435,6 +10435,18 @@
   </si>
   <si>
     <t>list_connectcases-action-</t>
+  </si>
+  <si>
+    <t>AWS End User Messaging</t>
+  </si>
+  <si>
+    <t>list_endusermessaging.html</t>
+  </si>
+  <si>
+    <t>end-user-messaging</t>
+  </si>
+  <si>
+    <t>list_endusermessaging-action-</t>
   </si>
 </sst>
 </file>
@@ -11382,7 +11394,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:D478"/>
+  <dimension ref="A1:D479"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -14963,1943 +14975,1957 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>894</v>
+        <v>3465</v>
       </c>
       <c r="B313" t="s">
-        <v>413</v>
-      </c>
-      <c r="C313" s="9" t="s">
-        <v>895</v>
-      </c>
-      <c r="D313" s="9" t="s">
-        <v>3419</v>
+        <v>3467</v>
+      </c>
+      <c r="C313" t="s">
+        <v>3466</v>
+      </c>
+      <c r="D313" t="s">
+        <v>3468</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B314" t="s">
-        <v>897</v>
+        <v>413</v>
       </c>
       <c r="C314" s="9" t="s">
-        <v>3385</v>
+        <v>895</v>
       </c>
       <c r="D314" s="9" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B315" t="s">
-        <v>899</v>
-      </c>
-      <c r="C315" t="s">
-        <v>900</v>
+        <v>897</v>
+      </c>
+      <c r="C315" s="9" t="s">
+        <v>3385</v>
+      </c>
+      <c r="D315" s="9" t="s">
+        <v>3420</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B316" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C316" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B317" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="C317" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B318" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="C318" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B319" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="C319" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="B320" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C320" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="B321" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C321" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B322" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C322" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B323" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C323" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="B324" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="C324" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B325" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="C325" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B326" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="C326" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B327" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C327" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B328" t="s">
-        <v>938</v>
-      </c>
-      <c r="C328" s="9" t="s">
-        <v>3347</v>
-      </c>
-      <c r="D328" s="9" t="s">
-        <v>3421</v>
+        <v>935</v>
+      </c>
+      <c r="C328" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B329" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C329" s="9" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="D329" s="9" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B330" t="s">
-        <v>942</v>
-      </c>
-      <c r="C330" t="s">
-        <v>943</v>
+        <v>940</v>
+      </c>
+      <c r="C330" s="9" t="s">
+        <v>3348</v>
+      </c>
+      <c r="D330" s="9" t="s">
+        <v>3422</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B331" t="s">
-        <v>945</v>
-      </c>
-      <c r="C331" s="9" t="s">
-        <v>3349</v>
-      </c>
-      <c r="D331" s="9" t="s">
-        <v>3423</v>
+        <v>942</v>
+      </c>
+      <c r="C331" t="s">
+        <v>943</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B332" t="s">
-        <v>947</v>
-      </c>
-      <c r="C332" t="s">
-        <v>948</v>
+        <v>945</v>
+      </c>
+      <c r="C332" s="9" t="s">
+        <v>3349</v>
+      </c>
+      <c r="D332" s="9" t="s">
+        <v>3423</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B333" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="C333" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B334" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="C334" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B335" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="C335" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="B336" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="C336" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B337" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="C337" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B338" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C338" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B339" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="C339" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B340" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C340" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B341" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="C341" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B342" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="C342" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B343" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="C343" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B344" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="C344" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B345" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C345" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B346" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="C346" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B347" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="C347" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="B348" t="s">
         <v>992</v>
       </c>
       <c r="C348" t="s">
-        <v>995</v>
-      </c>
-      <c r="D348" s="9" t="s">
-        <v>3424</v>
+        <v>993</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B349" t="s">
-        <v>997</v>
-      </c>
-      <c r="C349" s="9" t="s">
-        <v>3350</v>
+        <v>992</v>
+      </c>
+      <c r="C349" t="s">
+        <v>995</v>
       </c>
       <c r="D349" s="9" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B350" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C350" s="9" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="D350" s="9" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B351" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C351" t="s">
-        <v>1002</v>
+        <v>999</v>
+      </c>
+      <c r="C351" s="9" t="s">
+        <v>3351</v>
+      </c>
+      <c r="D351" s="9" t="s">
+        <v>3426</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="B352" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="C352" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B353" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="C353" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="B354" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="C354" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="B355" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="C355" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B356" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C356" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B357" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="C357" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="B358" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="C358" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B359" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C359" s="9" t="s">
-        <v>3352</v>
-      </c>
-      <c r="D359" s="9" t="s">
-        <v>3427</v>
+        <v>1022</v>
+      </c>
+      <c r="C359" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B360" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C360" t="s">
-        <v>1028</v>
+        <v>1025</v>
+      </c>
+      <c r="C360" s="9" t="s">
+        <v>3352</v>
+      </c>
+      <c r="D360" s="9" t="s">
+        <v>3427</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="B361" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="C361" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B362" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="C362" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B363" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="C363" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="B364" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="C364" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="B365" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="C365" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D365" s="9" t="s">
-        <v>3428</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B366" t="s">
         <v>1042</v>
       </c>
       <c r="C366" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D366" t="s">
-        <v>3460</v>
+        <v>1043</v>
+      </c>
+      <c r="D366" s="9" t="s">
+        <v>3428</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B367" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="C367" t="s">
-        <v>1048</v>
+        <v>1045</v>
+      </c>
+      <c r="D367" t="s">
+        <v>3460</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="B368" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="C368" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D368" s="9" t="s">
-        <v>3429</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B369" t="s">
         <v>1042</v>
       </c>
       <c r="C369" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D369" s="9" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B370" t="s">
         <v>1042</v>
       </c>
       <c r="C370" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D370" t="s">
-        <v>3461</v>
+        <v>1052</v>
+      </c>
+      <c r="D370" s="9" t="s">
+        <v>3430</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B371" t="s">
         <v>1042</v>
       </c>
       <c r="C371" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D371" s="9" t="s">
-        <v>3431</v>
+        <v>1054</v>
+      </c>
+      <c r="D371" t="s">
+        <v>3461</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B372" t="s">
-        <v>1058</v>
+        <v>1042</v>
       </c>
       <c r="C372" t="s">
-        <v>1059</v>
+        <v>1056</v>
+      </c>
+      <c r="D372" s="9" t="s">
+        <v>3431</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="B373" t="s">
-        <v>1042</v>
+        <v>1058</v>
       </c>
       <c r="C373" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D373" s="9" t="s">
-        <v>3432</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B374" t="s">
         <v>1042</v>
       </c>
       <c r="C374" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D374" s="9" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B375" t="s">
         <v>1042</v>
       </c>
       <c r="C375" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="D375" s="9" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B376" t="s">
         <v>1042</v>
       </c>
       <c r="C376" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="D376" s="9" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B377" t="s">
         <v>1042</v>
       </c>
       <c r="C377" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D377" s="9" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B378" t="s">
-        <v>1071</v>
+        <v>1042</v>
       </c>
       <c r="C378" t="s">
-        <v>1072</v>
+        <v>1069</v>
+      </c>
+      <c r="D378" s="9" t="s">
+        <v>3436</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="B379" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C379" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B380" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="C380" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="B381" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C381" s="9" t="s">
-        <v>3353</v>
-      </c>
-      <c r="D381" s="9" t="s">
-        <v>3437</v>
+        <v>1077</v>
+      </c>
+      <c r="C381" t="s">
+        <v>1078</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B382" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C382" s="9" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="D382" s="9" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B383" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C383" s="9" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="D383" s="9" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B384" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C384" s="9" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="D384" s="9" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B385" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C385" s="9" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="D385" s="9" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B386" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C386" t="s">
-        <v>1091</v>
+        <v>1088</v>
+      </c>
+      <c r="C386" s="9" t="s">
+        <v>3357</v>
+      </c>
+      <c r="D386" s="9" t="s">
+        <v>3441</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="B387" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="C387" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="B388" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="C388" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="B389" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C389" s="9" t="s">
-        <v>3358</v>
-      </c>
-      <c r="D389" s="9" t="s">
-        <v>3442</v>
+        <v>1096</v>
+      </c>
+      <c r="C389" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B390" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C390" t="s">
-        <v>1102</v>
+        <v>1099</v>
+      </c>
+      <c r="C390" s="9" t="s">
+        <v>3358</v>
+      </c>
+      <c r="D390" s="9" t="s">
+        <v>3442</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="B391" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="C391" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="B392" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="C392" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="B393" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="C393" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="B394" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="C394" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B395" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="C395" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="B396" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C396" s="9" t="s">
-        <v>3359</v>
-      </c>
-      <c r="D396" s="9" t="s">
-        <v>3443</v>
+        <v>1116</v>
+      </c>
+      <c r="C396" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B397" t="s">
-        <v>1121</v>
-      </c>
-      <c r="C397" t="s">
-        <v>1122</v>
+        <v>1119</v>
+      </c>
+      <c r="C397" s="9" t="s">
+        <v>3359</v>
+      </c>
+      <c r="D397" s="9" t="s">
+        <v>3443</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B398" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C398" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B399" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="C399" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="B400" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C400" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B401" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C401" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="B402" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C402" s="9" t="s">
-        <v>3360</v>
-      </c>
-      <c r="D402" s="9" t="s">
-        <v>3444</v>
+        <v>1133</v>
+      </c>
+      <c r="C402" t="s">
+        <v>1134</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B403" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C403" t="s">
-        <v>1139</v>
+        <v>1136</v>
+      </c>
+      <c r="C403" s="9" t="s">
+        <v>3360</v>
+      </c>
+      <c r="D403" s="9" t="s">
+        <v>3444</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="B404" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="C404" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B405" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="C405" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B406" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="C406" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="B407" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="C407" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="B408" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="C408" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B409" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="C409" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="B410" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="C410" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="B411" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="C411" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="B412" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C412" s="9" t="s">
-        <v>3361</v>
-      </c>
-      <c r="D412" s="9" t="s">
-        <v>3445</v>
+        <v>1162</v>
+      </c>
+      <c r="C412" t="s">
+        <v>1163</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="B413" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C413" t="s">
-        <v>1168</v>
+        <v>1165</v>
+      </c>
+      <c r="C413" s="9" t="s">
+        <v>3361</v>
+      </c>
+      <c r="D413" s="9" t="s">
+        <v>3445</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="B414" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="C414" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="B415" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="C415" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="B416" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="C416" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="B417" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="C417" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="B418" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="C418" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="B419" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="C419" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B420" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="C420" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="B421" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C421" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B422" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="C422" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="B423" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="C423" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="B424" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="C424" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="B425" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="C425" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B426" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="C426" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="B427" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="C427" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="B428" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C428" s="9" t="s">
-        <v>3362</v>
-      </c>
-      <c r="D428" s="9" t="s">
-        <v>3446</v>
+        <v>1209</v>
+      </c>
+      <c r="C428" t="s">
+        <v>1210</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B429" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C429" t="s">
-        <v>1215</v>
+        <v>1212</v>
+      </c>
+      <c r="C429" s="9" t="s">
+        <v>3362</v>
+      </c>
+      <c r="D429" s="9" t="s">
+        <v>3446</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="B430" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="C430" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B431" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="C431" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="B432" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="C432" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="B433" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="C433" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="B434" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="C434" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="B435" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="C435" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="B436" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="C436" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="B437" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="C437" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="B438" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C438" s="9" t="s">
-        <v>3363</v>
-      </c>
-      <c r="D438" s="9" t="s">
-        <v>3447</v>
+        <v>1238</v>
+      </c>
+      <c r="C438" t="s">
+        <v>1239</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B439" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C439" s="9" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D439" s="9" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B440" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C440" t="s">
-        <v>1246</v>
+        <v>1243</v>
+      </c>
+      <c r="C440" s="9" t="s">
+        <v>3364</v>
+      </c>
+      <c r="D440" s="9" t="s">
+        <v>3448</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="B441" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C441" s="9" t="s">
-        <v>3365</v>
-      </c>
-      <c r="D441" s="9" t="s">
-        <v>3449</v>
+        <v>1245</v>
+      </c>
+      <c r="C441" t="s">
+        <v>1246</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="B442" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C442" t="s">
-        <v>1251</v>
+        <v>1248</v>
+      </c>
+      <c r="C442" s="9" t="s">
+        <v>3365</v>
+      </c>
+      <c r="D442" s="9" t="s">
+        <v>3449</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="B443" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C443" s="9" t="s">
-        <v>3366</v>
-      </c>
-      <c r="D443" s="9" t="s">
-        <v>3450</v>
+        <v>1250</v>
+      </c>
+      <c r="C443" t="s">
+        <v>1251</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B444" t="s">
-        <v>1255</v>
-      </c>
-      <c r="C444" t="s">
-        <v>1256</v>
+        <v>1253</v>
+      </c>
+      <c r="C444" s="9" t="s">
+        <v>3366</v>
+      </c>
+      <c r="D444" s="9" t="s">
+        <v>3450</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="B445" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="C445" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="B446" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C446" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="B447" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="C447" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="B448" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="C448" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="B449" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="C449" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="B450" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="C450" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="B451" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="C451" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B452" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="C452" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="B453" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="C453" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="B454" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C454" s="9" t="s">
-        <v>3367</v>
-      </c>
-      <c r="D454" s="9" t="s">
-        <v>3451</v>
+        <v>1282</v>
+      </c>
+      <c r="C454" t="s">
+        <v>1283</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B455" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C455" t="s">
-        <v>1288</v>
+        <v>1285</v>
+      </c>
+      <c r="C455" s="9" t="s">
+        <v>3367</v>
+      </c>
+      <c r="D455" s="9" t="s">
+        <v>3451</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="B456" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="C456" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="B457" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="C457" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="B458" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="C458" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="B459" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="C459" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="B460" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="C460" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="B461" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="C461" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="B462" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="C462" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="B463" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C463" s="9" t="s">
-        <v>3368</v>
-      </c>
-      <c r="D463" s="9" t="s">
-        <v>3452</v>
+        <v>1308</v>
+      </c>
+      <c r="C463" t="s">
+        <v>1309</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B464" t="s">
-        <v>1313</v>
-      </c>
-      <c r="C464" t="s">
-        <v>1314</v>
+        <v>1311</v>
+      </c>
+      <c r="C464" s="9" t="s">
+        <v>3368</v>
+      </c>
+      <c r="D464" s="9" t="s">
+        <v>3452</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="B465" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="C465" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="B466" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C466" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="B467" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="C467" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="B468" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="C468" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="B469" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="C469" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="B470" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="C470" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="B471" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="C471" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="B472" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="C472" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="B473" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="C473" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="B474" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="C474" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="B475" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="C475" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="B476" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="C476" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="B477" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C477" s="9" t="s">
-        <v>3386</v>
-      </c>
-      <c r="D477" s="9" t="s">
-        <v>3453</v>
+        <v>1349</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C478" s="9" t="s">
+        <v>3386</v>
+      </c>
+      <c r="D478" s="9" t="s">
+        <v>3453</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A479" t="s">
         <v>1353</v>
       </c>
-      <c r="B478" t="s">
+      <c r="B479" t="s">
         <v>1354</v>
       </c>
-      <c r="C478" t="s">
+      <c r="C479" t="s">
         <v>1355</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D478" xr:uid="{DFA6D8D1-0167-4E54-B70B-9E1843D43EDB}"/>
+  <autoFilter ref="A1:D479" xr:uid="{DFA6D8D1-0167-4E54-B70B-9E1843D43EDB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
